--- a/Aula_14/banco2.xlsx
+++ b/Aula_14/banco2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jaoo</t>
+          <t>joa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -469,31 +469,7 @@
         <v>401</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>joao</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>321</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>poupança</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>402</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
+        <v>2020.2</v>
       </c>
     </row>
   </sheetData>

--- a/Aula_14/banco2.xlsx
+++ b/Aula_14/banco2.xlsx
@@ -469,7 +469,7 @@
         <v>401</v>
       </c>
       <c r="F2" t="n">
-        <v>2020.2</v>
+        <v>2017.575</v>
       </c>
     </row>
   </sheetData>
